--- a/resources/M673/spc_cpk_detail.xlsx
+++ b/resources/M673/spc_cpk_detail.xlsx
@@ -1147,10 +1147,10 @@
         <v>46186.35649305556</v>
       </c>
       <c r="J8">
-        <v>2.738158318627586</v>
+        <v>2.738158318627585</v>
       </c>
       <c r="K8">
-        <v>2.738158318627586</v>
+        <v>2.738158318627585</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1182,10 +1182,10 @@
         <v>46186.35649305556</v>
       </c>
       <c r="J9">
-        <v>2.738158318627586</v>
+        <v>2.738158318627585</v>
       </c>
       <c r="K9">
-        <v>2.738158318627586</v>
+        <v>2.738158318627585</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1217,10 +1217,10 @@
         <v>46186.35649305556</v>
       </c>
       <c r="J10">
-        <v>2.738158318627586</v>
+        <v>2.738158318627585</v>
       </c>
       <c r="K10">
-        <v>2.738158318627586</v>
+        <v>2.738158318627585</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1917,10 +1917,10 @@
         <v>46176.23791666667</v>
       </c>
       <c r="J30">
-        <v>1.681515102673519</v>
+        <v>1.68151510267352</v>
       </c>
       <c r="K30">
-        <v>1.681515102673519</v>
+        <v>1.68151510267352</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1987,10 +1987,10 @@
         <v>46176.23791666667</v>
       </c>
       <c r="J32">
-        <v>1.681515102673519</v>
+        <v>1.68151510267352</v>
       </c>
       <c r="K32">
-        <v>1.681515102673519</v>
+        <v>1.68151510267352</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2757,10 +2757,10 @@
         <v>46178.24862268518</v>
       </c>
       <c r="J54">
-        <v>2.022592903992482</v>
+        <v>2.022592903992483</v>
       </c>
       <c r="K54">
-        <v>2.022592903992482</v>
+        <v>2.022592903992483</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2792,10 +2792,10 @@
         <v>46178.24862268518</v>
       </c>
       <c r="J55">
-        <v>2.022592903992482</v>
+        <v>2.022592903992483</v>
       </c>
       <c r="K55">
-        <v>2.022592903992482</v>
+        <v>2.022592903992483</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -3107,10 +3107,10 @@
         <v>46194.03321759259</v>
       </c>
       <c r="J64">
-        <v>3.180235784917313</v>
+        <v>3.180235784917312</v>
       </c>
       <c r="K64">
-        <v>3.180235784917313</v>
+        <v>3.180235784917312</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -4612,10 +4612,10 @@
         <v>46197.27453703704</v>
       </c>
       <c r="J107">
-        <v>1.614968523946099</v>
+        <v>1.614968523946098</v>
       </c>
       <c r="K107">
-        <v>1.614968523946099</v>
+        <v>1.614968523946098</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -4647,10 +4647,10 @@
         <v>46197.27453703704</v>
       </c>
       <c r="J108">
-        <v>1.614968523946099</v>
+        <v>1.614968523946098</v>
       </c>
       <c r="K108">
-        <v>1.614968523946099</v>
+        <v>1.614968523946098</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -4682,10 +4682,10 @@
         <v>46197.27453703704</v>
       </c>
       <c r="J109">
-        <v>1.614968523946099</v>
+        <v>1.614968523946098</v>
       </c>
       <c r="K109">
-        <v>1.614968523946099</v>
+        <v>1.614968523946098</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -6922,10 +6922,10 @@
         <v>46201.95248842592</v>
       </c>
       <c r="J173">
-        <v>1.410629289262962</v>
+        <v>1.410629289262961</v>
       </c>
       <c r="K173">
-        <v>1.410629289262962</v>
+        <v>1.410629289262961</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -7342,10 +7342,10 @@
         <v>46194.95880787037</v>
       </c>
       <c r="J185">
-        <v>5.028760105203183</v>
+        <v>5.028760105203182</v>
       </c>
       <c r="K185">
-        <v>5.028760105203183</v>
+        <v>5.028760105203182</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -7412,10 +7412,10 @@
         <v>46194.95880787037</v>
       </c>
       <c r="J187">
-        <v>5.028760105203183</v>
+        <v>5.028760105203182</v>
       </c>
       <c r="K187">
-        <v>5.028760105203183</v>
+        <v>5.028760105203182</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -7622,10 +7622,10 @@
         <v>46203.15606481482</v>
       </c>
       <c r="J193">
-        <v>3.226144819218952</v>
+        <v>3.226144819218953</v>
       </c>
       <c r="K193">
-        <v>3.226144819218952</v>
+        <v>3.226144819218953</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -7902,10 +7902,10 @@
         <v>46200.59377314815</v>
       </c>
       <c r="J201">
-        <v>1.352595113591798</v>
+        <v>1.352595113591797</v>
       </c>
       <c r="K201">
-        <v>1.352595113591798</v>
+        <v>1.352595113591797</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -8042,10 +8042,10 @@
         <v>46194.50543981481</v>
       </c>
       <c r="J205">
-        <v>1.465543919435658</v>
+        <v>1.465543919435659</v>
       </c>
       <c r="K205">
-        <v>1.465543919435658</v>
+        <v>1.465543919435659</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -8077,10 +8077,10 @@
         <v>46200.59377314815</v>
       </c>
       <c r="J206">
-        <v>1.352595113591798</v>
+        <v>1.352595113591797</v>
       </c>
       <c r="K206">
-        <v>1.352595113591798</v>
+        <v>1.352595113591797</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -9267,10 +9267,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J240">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
       <c r="K240">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -9372,10 +9372,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J243">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
       <c r="K243">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -9477,10 +9477,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J246">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
       <c r="K246">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -9547,10 +9547,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J248">
-        <v>0.9608753676365078</v>
+        <v>0.960875367636508</v>
       </c>
       <c r="K248">
-        <v>0.9608753676365078</v>
+        <v>0.960875367636508</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -9652,10 +9652,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J251">
-        <v>0.9608753676365078</v>
+        <v>0.960875367636508</v>
       </c>
       <c r="K251">
-        <v>0.9608753676365078</v>
+        <v>0.960875367636508</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -9757,10 +9757,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J254">
-        <v>0.9608753676365078</v>
+        <v>0.960875367636508</v>
       </c>
       <c r="K254">
-        <v>0.9608753676365078</v>
+        <v>0.960875367636508</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -10107,10 +10107,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J264">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
       <c r="K264">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -10212,10 +10212,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J267">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
       <c r="K267">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -10317,10 +10317,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J270">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
       <c r="K270">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -11017,10 +11017,10 @@
         <v>46198.41539351852</v>
       </c>
       <c r="J290">
-        <v>1.576606407531863</v>
+        <v>1.576606407531862</v>
       </c>
       <c r="K290">
-        <v>1.576606407531863</v>
+        <v>1.576606407531862</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -11122,10 +11122,10 @@
         <v>46198.41539351852</v>
       </c>
       <c r="J293">
-        <v>1.576606407531863</v>
+        <v>1.576606407531862</v>
       </c>
       <c r="K293">
-        <v>1.576606407531863</v>
+        <v>1.576606407531862</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -11577,10 +11577,10 @@
         <v>46198.41539351852</v>
       </c>
       <c r="J306">
-        <v>1.354370578490787</v>
+        <v>1.354370578490788</v>
       </c>
       <c r="K306">
-        <v>1.354370578490787</v>
+        <v>1.354370578490788</v>
       </c>
     </row>
     <row r="307" spans="1:11">
@@ -11682,10 +11682,10 @@
         <v>46198.41539351852</v>
       </c>
       <c r="J309">
-        <v>1.354370578490787</v>
+        <v>1.354370578490788</v>
       </c>
       <c r="K309">
-        <v>1.354370578490787</v>
+        <v>1.354370578490788</v>
       </c>
     </row>
     <row r="310" spans="1:11">
@@ -12032,10 +12032,10 @@
         <v>46198.41539351852</v>
       </c>
       <c r="J319">
-        <v>1.579589033707567</v>
+        <v>1.579589033707568</v>
       </c>
       <c r="K319">
-        <v>1.579589033707567</v>
+        <v>1.579589033707568</v>
       </c>
     </row>
     <row r="320" spans="1:11">
@@ -14062,10 +14062,10 @@
         <v>46188.31006944444</v>
       </c>
       <c r="J377">
-        <v>1.996569932722299</v>
+        <v>1.996569932722298</v>
       </c>
       <c r="K377">
-        <v>1.996569932722299</v>
+        <v>1.996569932722298</v>
       </c>
     </row>
     <row r="378" spans="1:11">
@@ -14132,10 +14132,10 @@
         <v>46188.31006944444</v>
       </c>
       <c r="J379">
-        <v>1.996569932722299</v>
+        <v>1.996569932722298</v>
       </c>
       <c r="K379">
-        <v>1.996569932722299</v>
+        <v>1.996569932722298</v>
       </c>
     </row>
     <row r="380" spans="1:11">
@@ -14622,10 +14622,10 @@
         <v>46175.59159722222</v>
       </c>
       <c r="J393">
-        <v>1.469936415465094</v>
+        <v>1.469936415465095</v>
       </c>
       <c r="K393">
-        <v>1.469936415465094</v>
+        <v>1.469936415465095</v>
       </c>
     </row>
     <row r="394" spans="1:11">
@@ -14657,10 +14657,10 @@
         <v>46187.7934837963</v>
       </c>
       <c r="J394">
-        <v>1.830778503192253</v>
+        <v>1.830778503192254</v>
       </c>
       <c r="K394">
-        <v>1.830778503192253</v>
+        <v>1.830778503192254</v>
       </c>
     </row>
     <row r="395" spans="1:11">
@@ -14727,10 +14727,10 @@
         <v>46196.21538194444</v>
       </c>
       <c r="J396">
-        <v>1.671729950410031</v>
+        <v>1.671729950410032</v>
       </c>
       <c r="K396">
-        <v>1.671729950410031</v>
+        <v>1.671729950410032</v>
       </c>
     </row>
     <row r="397" spans="1:11">
@@ -14797,10 +14797,10 @@
         <v>46175.59159722222</v>
       </c>
       <c r="J398">
-        <v>1.469936415465094</v>
+        <v>1.469936415465095</v>
       </c>
       <c r="K398">
-        <v>1.469936415465094</v>
+        <v>1.469936415465095</v>
       </c>
     </row>
     <row r="399" spans="1:11">
@@ -14832,10 +14832,10 @@
         <v>46187.7934837963</v>
       </c>
       <c r="J399">
-        <v>1.830778503192253</v>
+        <v>1.830778503192254</v>
       </c>
       <c r="K399">
-        <v>1.830778503192253</v>
+        <v>1.830778503192254</v>
       </c>
     </row>
     <row r="400" spans="1:11">
@@ -14902,10 +14902,10 @@
         <v>46196.21538194444</v>
       </c>
       <c r="J401">
-        <v>1.671729950410031</v>
+        <v>1.671729950410032</v>
       </c>
       <c r="K401">
-        <v>1.671729950410031</v>
+        <v>1.671729950410032</v>
       </c>
     </row>
     <row r="402" spans="1:11">
@@ -15497,10 +15497,10 @@
         <v>46204.32052083333</v>
       </c>
       <c r="J418">
-        <v>1.453814216762429</v>
+        <v>1.453814216762428</v>
       </c>
       <c r="K418">
-        <v>1.453814216762429</v>
+        <v>1.453814216762428</v>
       </c>
     </row>
     <row r="419" spans="1:11">
@@ -15567,10 +15567,10 @@
         <v>46204.32052083333</v>
       </c>
       <c r="J420">
-        <v>1.453814216762429</v>
+        <v>1.453814216762428</v>
       </c>
       <c r="K420">
-        <v>1.453814216762429</v>
+        <v>1.453814216762428</v>
       </c>
     </row>
     <row r="421" spans="1:11">
@@ -15637,10 +15637,10 @@
         <v>46204.32052083333</v>
       </c>
       <c r="J422">
-        <v>1.453814216762429</v>
+        <v>1.453814216762428</v>
       </c>
       <c r="K422">
-        <v>1.453814216762429</v>
+        <v>1.453814216762428</v>
       </c>
     </row>
     <row r="423" spans="1:11">
@@ -16512,10 +16512,10 @@
         <v>46192.56226851852</v>
       </c>
       <c r="J447">
-        <v>2.983692266702674</v>
+        <v>2.983692266702675</v>
       </c>
       <c r="K447">
-        <v>2.983692266702674</v>
+        <v>2.983692266702675</v>
       </c>
     </row>
     <row r="448" spans="1:11">
@@ -16547,10 +16547,10 @@
         <v>46193.80456018518</v>
       </c>
       <c r="J448">
-        <v>2.741789175656586</v>
+        <v>2.741789175656585</v>
       </c>
       <c r="K448">
-        <v>2.741789175656586</v>
+        <v>2.741789175656585</v>
       </c>
     </row>
     <row r="449" spans="1:11">
@@ -17037,10 +17037,10 @@
         <v>46182.20199074074</v>
       </c>
       <c r="J462">
-        <v>4.52469064847966</v>
+        <v>4.524690648479659</v>
       </c>
       <c r="K462">
-        <v>4.52469064847966</v>
+        <v>4.524690648479659</v>
       </c>
     </row>
     <row r="463" spans="1:11">
@@ -17142,10 +17142,10 @@
         <v>46207.94072916666</v>
       </c>
       <c r="J465">
-        <v>2.894247413257618</v>
+        <v>2.894247413257619</v>
       </c>
       <c r="K465">
-        <v>2.894247413257618</v>
+        <v>2.894247413257619</v>
       </c>
     </row>
     <row r="466" spans="1:11">
@@ -17317,10 +17317,10 @@
         <v>46216.98412037037</v>
       </c>
       <c r="J470">
-        <v>3.578093581579563</v>
+        <v>3.578093581579564</v>
       </c>
       <c r="K470">
-        <v>3.578093581579563</v>
+        <v>3.578093581579564</v>
       </c>
     </row>
     <row r="471" spans="1:11">
@@ -17352,10 +17352,10 @@
         <v>46217.94935185185</v>
       </c>
       <c r="J471">
-        <v>3.190334845233488</v>
+        <v>3.190334845233487</v>
       </c>
       <c r="K471">
-        <v>3.190334845233488</v>
+        <v>3.190334845233487</v>
       </c>
     </row>
     <row r="472" spans="1:11">
@@ -17807,10 +17807,10 @@
         <v>46179.92976851852</v>
       </c>
       <c r="J484">
-        <v>1.785766343947263</v>
+        <v>1.785766343947262</v>
       </c>
       <c r="K484">
-        <v>1.785766343947263</v>
+        <v>1.785766343947262</v>
       </c>
     </row>
     <row r="485" spans="1:11">
@@ -18262,10 +18262,10 @@
         <v>46218.94015046296</v>
       </c>
       <c r="J497">
-        <v>1.786654295857735</v>
+        <v>1.786654295857736</v>
       </c>
       <c r="K497">
-        <v>1.786654295857735</v>
+        <v>1.786654295857736</v>
       </c>
     </row>
     <row r="498" spans="1:11">
@@ -18332,10 +18332,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J499">
-        <v>1.957942972983792</v>
+        <v>1.957942972983791</v>
       </c>
       <c r="K499">
-        <v>1.957942972983792</v>
+        <v>1.957942972983791</v>
       </c>
     </row>
     <row r="500" spans="1:11">
@@ -18577,10 +18577,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J506">
-        <v>3.363165505438486</v>
+        <v>3.363165505438485</v>
       </c>
       <c r="K506">
-        <v>3.363165505438486</v>
+        <v>3.363165505438485</v>
       </c>
     </row>
     <row r="507" spans="1:11">
@@ -18787,10 +18787,10 @@
         <v>46182.20199074074</v>
       </c>
       <c r="J512">
-        <v>4.83877651601209</v>
+        <v>4.838776516012089</v>
       </c>
       <c r="K512">
-        <v>4.83877651601209</v>
+        <v>4.838776516012089</v>
       </c>
     </row>
     <row r="513" spans="1:11">
@@ -18962,10 +18962,10 @@
         <v>46209.80684027778</v>
       </c>
       <c r="J517">
-        <v>4.241939324748977</v>
+        <v>4.241939324748978</v>
       </c>
       <c r="K517">
-        <v>4.241939324748977</v>
+        <v>4.241939324748978</v>
       </c>
     </row>
     <row r="518" spans="1:11">
@@ -19207,10 +19207,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J524">
-        <v>3.743229372061784</v>
+        <v>3.743229372061785</v>
       </c>
       <c r="K524">
-        <v>3.743229372061784</v>
+        <v>3.743229372061785</v>
       </c>
     </row>
     <row r="525" spans="1:11">
@@ -19697,10 +19697,10 @@
         <v>46205.8512962963</v>
       </c>
       <c r="J538">
-        <v>1.787298381054458</v>
+        <v>1.787298381054459</v>
       </c>
       <c r="K538">
-        <v>1.787298381054458</v>
+        <v>1.787298381054459</v>
       </c>
     </row>
     <row r="539" spans="1:11">
@@ -19767,10 +19767,10 @@
         <v>46207.94072916666</v>
       </c>
       <c r="J540">
-        <v>2.191797453450521</v>
+        <v>2.191797453450522</v>
       </c>
       <c r="K540">
-        <v>2.191797453450521</v>
+        <v>2.191797453450522</v>
       </c>
     </row>
     <row r="541" spans="1:11">
@@ -20012,10 +20012,10 @@
         <v>46218.94015046296</v>
       </c>
       <c r="J547">
-        <v>2.309536490869236</v>
+        <v>2.309536490869235</v>
       </c>
       <c r="K547">
-        <v>2.309536490869236</v>
+        <v>2.309536490869235</v>
       </c>
     </row>
     <row r="548" spans="1:11">
@@ -20222,10 +20222,10 @@
         <v>46182.20199074074</v>
       </c>
       <c r="J553">
-        <v>6.870986615177313</v>
+        <v>6.870986615177314</v>
       </c>
       <c r="K553">
-        <v>6.870986615177313</v>
+        <v>6.870986615177314</v>
       </c>
     </row>
     <row r="554" spans="1:11">
@@ -20502,10 +20502,10 @@
         <v>46181.77182870371</v>
       </c>
       <c r="J561">
-        <v>6.814148115317333</v>
+        <v>6.814148115317331</v>
       </c>
       <c r="K561">
-        <v>6.814148115317333</v>
+        <v>6.814148115317331</v>
       </c>
     </row>
     <row r="562" spans="1:11">
@@ -20572,10 +20572,10 @@
         <v>46205.8512962963</v>
       </c>
       <c r="J563">
-        <v>7.271296243534849</v>
+        <v>7.271296243534847</v>
       </c>
       <c r="K563">
-        <v>7.271296243534849</v>
+        <v>7.271296243534847</v>
       </c>
     </row>
     <row r="564" spans="1:11">
@@ -20817,10 +20817,10 @@
         <v>46216.98412037037</v>
       </c>
       <c r="J570">
-        <v>6.307311610990255</v>
+        <v>6.307311610990257</v>
       </c>
       <c r="K570">
-        <v>6.307311610990255</v>
+        <v>6.307311610990257</v>
       </c>
     </row>
     <row r="571" spans="1:11">
@@ -20852,10 +20852,10 @@
         <v>46217.94935185185</v>
       </c>
       <c r="J571">
-        <v>5.499474884178865</v>
+        <v>5.499474884178864</v>
       </c>
       <c r="K571">
-        <v>5.499474884178865</v>
+        <v>5.499474884178864</v>
       </c>
     </row>
     <row r="572" spans="1:11">
@@ -21307,10 +21307,10 @@
         <v>46179.92976851852</v>
       </c>
       <c r="J584">
-        <v>2.289085672177559</v>
+        <v>2.289085672177558</v>
       </c>
       <c r="K584">
-        <v>2.289085672177559</v>
+        <v>2.289085672177558</v>
       </c>
     </row>
     <row r="585" spans="1:11">
@@ -21622,10 +21622,10 @@
         <v>46210.60912037037</v>
       </c>
       <c r="J593">
-        <v>2.168945081637211</v>
+        <v>2.16894508163721</v>
       </c>
       <c r="K593">
-        <v>2.168945081637211</v>
+        <v>2.16894508163721</v>
       </c>
     </row>
     <row r="594" spans="1:11">
@@ -21692,10 +21692,10 @@
         <v>46216.98412037037</v>
       </c>
       <c r="J595">
-        <v>2.727288952899633</v>
+        <v>2.727288952899634</v>
       </c>
       <c r="K595">
-        <v>2.727288952899633</v>
+        <v>2.727288952899634</v>
       </c>
     </row>
     <row r="596" spans="1:11">
@@ -21797,10 +21797,10 @@
         <v>46219.73939814815</v>
       </c>
       <c r="J598">
-        <v>2.6636454511094</v>
+        <v>2.663645451109401</v>
       </c>
       <c r="K598">
-        <v>2.6636454511094</v>
+        <v>2.663645451109401</v>
       </c>
     </row>
     <row r="599" spans="1:11">
@@ -21972,10 +21972,10 @@
         <v>46182.08170138889</v>
       </c>
       <c r="J603">
-        <v>6.536125891785144</v>
+        <v>6.536125891785145</v>
       </c>
       <c r="K603">
-        <v>6.536125891785144</v>
+        <v>6.536125891785145</v>
       </c>
     </row>
     <row r="604" spans="1:11">
@@ -22077,10 +22077,10 @@
         <v>46220.03709490741</v>
       </c>
       <c r="J606">
-        <v>6.352550245936728</v>
+        <v>6.352550245936726</v>
       </c>
       <c r="K606">
-        <v>6.352550245936728</v>
+        <v>6.352550245936726</v>
       </c>
     </row>
     <row r="607" spans="1:11">
@@ -23302,10 +23302,10 @@
         <v>46211.14498842593</v>
       </c>
       <c r="J641">
-        <v>2.472828214414699</v>
+        <v>2.472828214414698</v>
       </c>
       <c r="K641">
-        <v>2.472828214414699</v>
+        <v>2.472828214414698</v>
       </c>
     </row>
     <row r="642" spans="1:11">
@@ -23967,10 +23967,10 @@
         <v>46207.86495370371</v>
       </c>
       <c r="J660">
-        <v>1.507303460676904</v>
+        <v>1.507303460676903</v>
       </c>
       <c r="K660">
-        <v>1.507303460676904</v>
+        <v>1.507303460676903</v>
       </c>
     </row>
     <row r="661" spans="1:11">
@@ -24072,10 +24072,10 @@
         <v>46210.9906712963</v>
       </c>
       <c r="J663">
-        <v>1.544973117046052</v>
+        <v>1.544973117046053</v>
       </c>
       <c r="K663">
-        <v>1.544973117046052</v>
+        <v>1.544973117046053</v>
       </c>
     </row>
     <row r="664" spans="1:11">
@@ -24142,10 +24142,10 @@
         <v>46217.99348379629</v>
       </c>
       <c r="J665">
-        <v>2.110247582543862</v>
+        <v>2.110247582543861</v>
       </c>
       <c r="K665">
-        <v>2.110247582543862</v>
+        <v>2.110247582543861</v>
       </c>
     </row>
     <row r="666" spans="1:11">
@@ -24422,10 +24422,10 @@
         <v>46208.97685185185</v>
       </c>
       <c r="J673">
-        <v>5.284726473752883</v>
+        <v>5.284726473752884</v>
       </c>
       <c r="K673">
-        <v>5.284726473752883</v>
+        <v>5.284726473752884</v>
       </c>
     </row>
     <row r="674" spans="1:11">
@@ -24912,10 +24912,10 @@
         <v>46211.14497685185</v>
       </c>
       <c r="J687">
-        <v>5.849518699950846</v>
+        <v>5.849518699950848</v>
       </c>
       <c r="K687">
-        <v>5.849518699950846</v>
+        <v>5.849518699950848</v>
       </c>
     </row>
     <row r="688" spans="1:11">
@@ -25332,10 +25332,10 @@
         <v>46175.20971064815</v>
       </c>
       <c r="J699">
-        <v>3.599368713017204</v>
+        <v>3.599368713017205</v>
       </c>
       <c r="K699">
-        <v>3.599368713017204</v>
+        <v>3.599368713017205</v>
       </c>
     </row>
     <row r="700" spans="1:11">
@@ -25717,10 +25717,10 @@
         <v>46211.14497685185</v>
       </c>
       <c r="J710">
-        <v>3.592327472601818</v>
+        <v>3.592327472601819</v>
       </c>
       <c r="K710">
-        <v>3.592327472601818</v>
+        <v>3.592327472601819</v>
       </c>
     </row>
     <row r="711" spans="1:11">
@@ -25857,10 +25857,10 @@
         <v>46220.03708333334</v>
       </c>
       <c r="J714">
-        <v>2.866682293405833</v>
+        <v>2.866682293405832</v>
       </c>
       <c r="K714">
-        <v>2.866682293405833</v>
+        <v>2.866682293405832</v>
       </c>
     </row>
     <row r="715" spans="1:11">
@@ -26942,10 +26942,10 @@
         <v>46175.20969907408</v>
       </c>
       <c r="J745">
-        <v>2.828155594301655</v>
+        <v>2.828155594301656</v>
       </c>
       <c r="K745">
-        <v>2.828155594301655</v>
+        <v>2.828155594301656</v>
       </c>
     </row>
     <row r="746" spans="1:11">
@@ -27327,10 +27327,10 @@
         <v>46211.14496527778</v>
       </c>
       <c r="J756">
-        <v>2.120311327915183</v>
+        <v>2.120311327915184</v>
       </c>
       <c r="K756">
-        <v>2.120311327915183</v>
+        <v>2.120311327915184</v>
       </c>
     </row>
     <row r="757" spans="1:11">
@@ -27397,10 +27397,10 @@
         <v>46218.99494212963</v>
       </c>
       <c r="J758">
-        <v>2.32304084432433</v>
+        <v>2.323040844324331</v>
       </c>
       <c r="K758">
-        <v>2.32304084432433</v>
+        <v>2.323040844324331</v>
       </c>
     </row>
     <row r="759" spans="1:11">
@@ -27712,10 +27712,10 @@
         <v>46220.03707175926</v>
       </c>
       <c r="J767">
-        <v>0.7867021626660747</v>
+        <v>0.7867021626660746</v>
       </c>
       <c r="K767">
-        <v>0.7867021626660747</v>
+        <v>0.7867021626660746</v>
       </c>
     </row>
     <row r="768" spans="1:11">
@@ -28062,10 +28062,10 @@
         <v>46209.56256944445</v>
       </c>
       <c r="J777">
-        <v>7.30056758482832</v>
+        <v>7.300567584828319</v>
       </c>
       <c r="K777">
-        <v>7.30056758482832</v>
+        <v>7.300567584828319</v>
       </c>
     </row>
     <row r="778" spans="1:11">
@@ -28167,10 +28167,10 @@
         <v>46217.99346064815</v>
       </c>
       <c r="J780">
-        <v>0.7080882148098424</v>
+        <v>0.7080882148098422</v>
       </c>
       <c r="K780">
-        <v>0.7080882148098424</v>
+        <v>0.7080882148098422</v>
       </c>
     </row>
     <row r="781" spans="1:11">
@@ -28587,10 +28587,10 @@
         <v>46183.10130787037</v>
       </c>
       <c r="J792">
-        <v>1.513587046777795</v>
+        <v>1.513587046777796</v>
       </c>
       <c r="K792">
-        <v>1.513587046777795</v>
+        <v>1.513587046777796</v>
       </c>
     </row>
     <row r="793" spans="1:11">
@@ -28657,10 +28657,10 @@
         <v>46183.10130787037</v>
       </c>
       <c r="J794">
-        <v>1.513587046777795</v>
+        <v>1.513587046777796</v>
       </c>
       <c r="K794">
-        <v>1.513587046777795</v>
+        <v>1.513587046777796</v>
       </c>
     </row>
     <row r="795" spans="1:11">
@@ -28692,10 +28692,10 @@
         <v>46211.9912962963</v>
       </c>
       <c r="J795">
-        <v>2.6839041742187</v>
+        <v>2.683904174218701</v>
       </c>
       <c r="K795">
-        <v>2.6839041742187</v>
+        <v>2.683904174218701</v>
       </c>
     </row>
     <row r="796" spans="1:11">
@@ -28762,10 +28762,10 @@
         <v>46183.10130787037</v>
       </c>
       <c r="J797">
-        <v>1.513587046777795</v>
+        <v>1.513587046777796</v>
       </c>
       <c r="K797">
-        <v>1.513587046777795</v>
+        <v>1.513587046777796</v>
       </c>
     </row>
     <row r="798" spans="1:11">
@@ -28797,10 +28797,10 @@
         <v>46211.9912962963</v>
       </c>
       <c r="J798">
-        <v>2.6839041742187</v>
+        <v>2.683904174218701</v>
       </c>
       <c r="K798">
-        <v>2.6839041742187</v>
+        <v>2.683904174218701</v>
       </c>
     </row>
     <row r="799" spans="1:11">
@@ -29392,10 +29392,10 @@
         <v>46224.64265046296</v>
       </c>
       <c r="J815">
-        <v>1.618078526923039</v>
+        <v>1.61807852692304</v>
       </c>
       <c r="K815">
-        <v>1.618078526923039</v>
+        <v>1.61807852692304</v>
       </c>
     </row>
     <row r="816" spans="1:11">
@@ -29742,10 +29742,10 @@
         <v>46176.37012731482</v>
       </c>
       <c r="J825">
-        <v>1.595786344427045</v>
+        <v>1.595786344427046</v>
       </c>
       <c r="K825">
-        <v>1.595786344427045</v>
+        <v>1.595786344427046</v>
       </c>
     </row>
     <row r="826" spans="1:11">
@@ -29812,10 +29812,10 @@
         <v>46176.37012731482</v>
       </c>
       <c r="J827">
-        <v>1.595786344427045</v>
+        <v>1.595786344427046</v>
       </c>
       <c r="K827">
-        <v>1.595786344427045</v>
+        <v>1.595786344427046</v>
       </c>
     </row>
     <row r="828" spans="1:11">
@@ -29882,10 +29882,10 @@
         <v>46176.37012731482</v>
       </c>
       <c r="J829">
-        <v>1.595786344427045</v>
+        <v>1.595786344427046</v>
       </c>
       <c r="K829">
-        <v>1.595786344427045</v>
+        <v>1.595786344427046</v>
       </c>
     </row>
     <row r="830" spans="1:11">
@@ -30057,10 +30057,10 @@
         <v>46177.22050925926</v>
       </c>
       <c r="J834">
-        <v>3.450768867600634</v>
+        <v>3.450768867600633</v>
       </c>
       <c r="K834">
-        <v>3.450768867600634</v>
+        <v>3.450768867600633</v>
       </c>
     </row>
     <row r="835" spans="1:11">
@@ -30162,10 +30162,10 @@
         <v>46177.22050925926</v>
       </c>
       <c r="J837">
-        <v>3.450768867600634</v>
+        <v>3.450768867600633</v>
       </c>
       <c r="K837">
-        <v>3.450768867600634</v>
+        <v>3.450768867600633</v>
       </c>
     </row>
     <row r="838" spans="1:11">
@@ -30547,10 +30547,10 @@
         <v>46209.24260416667</v>
       </c>
       <c r="J848">
-        <v>3.03138073350442</v>
+        <v>3.031380733504421</v>
       </c>
       <c r="K848">
-        <v>3.03138073350442</v>
+        <v>3.031380733504421</v>
       </c>
     </row>
     <row r="849" spans="1:11">
@@ -31247,10 +31247,10 @@
         <v>46223.11774305555</v>
       </c>
       <c r="J868">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
       <c r="K868">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
     </row>
     <row r="869" spans="1:11">
@@ -31387,10 +31387,10 @@
         <v>46223.11774305555</v>
       </c>
       <c r="J872">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
       <c r="K872">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
     </row>
     <row r="873" spans="1:11">

--- a/resources/M673/spc_cpk_detail.xlsx
+++ b/resources/M673/spc_cpk_detail.xlsx
@@ -1442,10 +1442,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J22">
-        <v>0.9525948303586942</v>
+        <v>0.952594830358694</v>
       </c>
       <c r="K22">
-        <v>0.9525948303586942</v>
+        <v>0.952594830358694</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1477,10 +1477,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J23">
-        <v>0.9525948303586942</v>
+        <v>0.952594830358694</v>
       </c>
       <c r="K23">
-        <v>0.9525948303586942</v>
+        <v>0.952594830358694</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1512,10 +1512,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J24">
-        <v>0.9525948303586942</v>
+        <v>0.952594830358694</v>
       </c>
       <c r="K24">
-        <v>0.9525948303586942</v>
+        <v>0.952594830358694</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1652,10 +1652,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J28">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
       <c r="K28">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1687,10 +1687,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J29">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
       <c r="K29">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1722,10 +1722,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J30">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
       <c r="K30">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1757,10 +1757,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J31">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
       <c r="K31">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1792,10 +1792,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J32">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
       <c r="K32">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1827,10 +1827,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J33">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
       <c r="K33">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3892,10 +3892,10 @@
         <v>46218.94015046296</v>
       </c>
       <c r="J92">
-        <v>3.235467172811131</v>
+        <v>3.235467172811132</v>
       </c>
       <c r="K92">
-        <v>3.235467172811131</v>
+        <v>3.235467172811132</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -4382,10 +4382,10 @@
         <v>46216.98412037037</v>
       </c>
       <c r="J106">
-        <v>2.103503458931063</v>
+        <v>2.103503458931062</v>
       </c>
       <c r="K106">
-        <v>2.103503458931063</v>
+        <v>2.103503458931062</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4522,10 +4522,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J110">
-        <v>1.957942972983791</v>
+        <v>1.957942972983792</v>
       </c>
       <c r="K110">
-        <v>1.957942972983791</v>
+        <v>1.957942972983792</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4592,10 +4592,10 @@
         <v>46208.89827546296</v>
       </c>
       <c r="J112">
-        <v>3.758325112538278</v>
+        <v>3.758325112538279</v>
       </c>
       <c r="K112">
-        <v>3.758325112538278</v>
+        <v>3.758325112538279</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -4662,10 +4662,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J114">
-        <v>3.363165505438485</v>
+        <v>3.363165505438486</v>
       </c>
       <c r="K114">
-        <v>3.363165505438485</v>
+        <v>3.363165505438486</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -4907,10 +4907,10 @@
         <v>46211.21850694445</v>
       </c>
       <c r="J121">
-        <v>3.743629151530029</v>
+        <v>3.74362915153003</v>
       </c>
       <c r="K121">
-        <v>3.743629151530029</v>
+        <v>3.74362915153003</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -5327,10 +5327,10 @@
         <v>46207.94072916666</v>
       </c>
       <c r="J133">
-        <v>2.191797453450522</v>
+        <v>2.191797453450521</v>
       </c>
       <c r="K133">
-        <v>2.191797453450522</v>
+        <v>2.191797453450521</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5817,10 +5817,10 @@
         <v>46205.8512962963</v>
       </c>
       <c r="J147">
-        <v>7.271296243534849</v>
+        <v>7.27129624353485</v>
       </c>
       <c r="K147">
-        <v>7.271296243534849</v>
+        <v>7.27129624353485</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -6097,10 +6097,10 @@
         <v>46217.94935185185</v>
       </c>
       <c r="J155">
-        <v>5.499474884178865</v>
+        <v>5.499474884178864</v>
       </c>
       <c r="K155">
-        <v>5.499474884178865</v>
+        <v>5.499474884178864</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -6167,10 +6167,10 @@
         <v>46219.73939814815</v>
       </c>
       <c r="J157">
-        <v>6.898914758144567</v>
+        <v>6.898914758144568</v>
       </c>
       <c r="K157">
-        <v>6.898914758144567</v>
+        <v>6.898914758144568</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -6202,10 +6202,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J158">
-        <v>6.49790428802241</v>
+        <v>6.497904288022408</v>
       </c>
       <c r="K158">
-        <v>6.49790428802241</v>
+        <v>6.497904288022408</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6377,10 +6377,10 @@
         <v>46205.8512962963</v>
       </c>
       <c r="J163">
-        <v>3.197210325160678</v>
+        <v>3.197210325160679</v>
       </c>
       <c r="K163">
-        <v>3.197210325160678</v>
+        <v>3.197210325160679</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -6552,10 +6552,10 @@
         <v>46210.60912037037</v>
       </c>
       <c r="J168">
-        <v>2.168945081637211</v>
+        <v>2.16894508163721</v>
       </c>
       <c r="K168">
-        <v>2.168945081637211</v>
+        <v>2.16894508163721</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -6622,10 +6622,10 @@
         <v>46216.98412037037</v>
       </c>
       <c r="J170">
-        <v>2.727288952899634</v>
+        <v>2.727288952899633</v>
       </c>
       <c r="K170">
-        <v>2.727288952899634</v>
+        <v>2.727288952899633</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -6832,10 +6832,10 @@
         <v>46208.97686342592</v>
       </c>
       <c r="J176">
-        <v>6.701960798400199</v>
+        <v>6.701960798400201</v>
       </c>
       <c r="K176">
-        <v>6.701960798400199</v>
+        <v>6.701960798400201</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -7182,10 +7182,10 @@
         <v>46217.99348379629</v>
       </c>
       <c r="J186">
-        <v>6.192348994696269</v>
+        <v>6.192348994696268</v>
       </c>
       <c r="K186">
-        <v>6.192348994696269</v>
+        <v>6.192348994696268</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -7602,10 +7602,10 @@
         <v>46209.56259259259</v>
       </c>
       <c r="J198">
-        <v>2.652272060164093</v>
+        <v>2.652272060164092</v>
       </c>
       <c r="K198">
-        <v>2.652272060164093</v>
+        <v>2.652272060164092</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -7672,10 +7672,10 @@
         <v>46211.14498842593</v>
       </c>
       <c r="J200">
-        <v>2.472828214414698</v>
+        <v>2.472828214414699</v>
       </c>
       <c r="K200">
-        <v>2.472828214414698</v>
+        <v>2.472828214414699</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -7952,10 +7952,10 @@
         <v>46220.03709490741</v>
       </c>
       <c r="J208">
-        <v>1.622592413978054</v>
+        <v>1.622592413978055</v>
       </c>
       <c r="K208">
-        <v>1.622592413978054</v>
+        <v>1.622592413978055</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -8057,10 +8057,10 @@
         <v>46207.86495370371</v>
       </c>
       <c r="J211">
-        <v>1.507303460676903</v>
+        <v>1.507303460676904</v>
       </c>
       <c r="K211">
-        <v>1.507303460676903</v>
+        <v>1.507303460676904</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -8232,10 +8232,10 @@
         <v>46217.99348379629</v>
       </c>
       <c r="J216">
-        <v>2.110247582543861</v>
+        <v>2.110247582543862</v>
       </c>
       <c r="K216">
-        <v>2.110247582543861</v>
+        <v>2.110247582543862</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -8407,10 +8407,10 @@
         <v>46208.97685185185</v>
       </c>
       <c r="J221">
-        <v>5.284726473752884</v>
+        <v>5.284726473752883</v>
       </c>
       <c r="K221">
-        <v>5.284726473752884</v>
+        <v>5.284726473752883</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -8617,10 +8617,10 @@
         <v>46208.97685185185</v>
       </c>
       <c r="J227">
-        <v>5.795279755351938</v>
+        <v>5.795279755351936</v>
       </c>
       <c r="K227">
-        <v>5.795279755351938</v>
+        <v>5.795279755351936</v>
       </c>
     </row>
     <row r="228" spans="1:11">
@@ -8722,10 +8722,10 @@
         <v>46211.14497685185</v>
       </c>
       <c r="J230">
-        <v>5.849518699950846</v>
+        <v>5.849518699950848</v>
       </c>
       <c r="K230">
-        <v>5.849518699950846</v>
+        <v>5.849518699950848</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -8792,10 +8792,10 @@
         <v>46218.9949537037</v>
       </c>
       <c r="J232">
-        <v>5.01237232238182</v>
+        <v>5.012372322381821</v>
       </c>
       <c r="K232">
-        <v>5.01237232238182</v>
+        <v>5.012372322381821</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -9387,10 +9387,10 @@
         <v>46220.03708333334</v>
       </c>
       <c r="J249">
-        <v>2.866682293405832</v>
+        <v>2.866682293405833</v>
       </c>
       <c r="K249">
-        <v>2.866682293405832</v>
+        <v>2.866682293405833</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -10367,10 +10367,10 @@
         <v>46218.99494212963</v>
       </c>
       <c r="J277">
-        <v>2.323040844324331</v>
+        <v>2.32304084432433</v>
       </c>
       <c r="K277">
-        <v>2.323040844324331</v>
+        <v>2.32304084432433</v>
       </c>
     </row>
     <row r="278" spans="1:11">
@@ -10752,10 +10752,10 @@
         <v>46209.56256944445</v>
       </c>
       <c r="J288">
-        <v>7.30056758482832</v>
+        <v>7.300567584828319</v>
       </c>
       <c r="K288">
-        <v>7.30056758482832</v>
+        <v>7.300567584828319</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -11347,10 +11347,10 @@
         <v>46225.2184837963</v>
       </c>
       <c r="J305">
-        <v>1.535772329774229</v>
+        <v>1.549961236506244</v>
       </c>
       <c r="K305">
-        <v>1.535772329774229</v>
+        <v>1.549961236506244</v>
       </c>
     </row>
     <row r="306" spans="1:11">
@@ -11452,10 +11452,10 @@
         <v>46225.2184837963</v>
       </c>
       <c r="J308">
-        <v>1.277659345360459</v>
+        <v>1.572344746850624</v>
       </c>
       <c r="K308">
-        <v>1.277659345360459</v>
+        <v>1.572344746850624</v>
       </c>
     </row>
     <row r="309" spans="1:11">
@@ -11627,10 +11627,10 @@
         <v>46225.2184837963</v>
       </c>
       <c r="J313">
-        <v>1.277659345360459</v>
+        <v>1.572344746850624</v>
       </c>
       <c r="K313">
-        <v>1.277659345360459</v>
+        <v>1.572344746850624</v>
       </c>
     </row>
     <row r="314" spans="1:11">
@@ -11662,10 +11662,10 @@
         <v>46224.64265046296</v>
       </c>
       <c r="J314">
-        <v>1.61807852692304</v>
+        <v>1.618078526923039</v>
       </c>
       <c r="K314">
-        <v>1.61807852692304</v>
+        <v>1.618078526923039</v>
       </c>
     </row>
     <row r="315" spans="1:11">
@@ -11697,10 +11697,10 @@
         <v>46208.79484953704</v>
       </c>
       <c r="J315">
-        <v>1.783027911356679</v>
+        <v>1.78302791135668</v>
       </c>
       <c r="K315">
-        <v>1.783027911356679</v>
+        <v>1.78302791135668</v>
       </c>
     </row>
     <row r="316" spans="1:11">
@@ -11767,10 +11767,10 @@
         <v>46208.79484953704</v>
       </c>
       <c r="J317">
-        <v>1.783027911356679</v>
+        <v>1.78302791135668</v>
       </c>
       <c r="K317">
-        <v>1.783027911356679</v>
+        <v>1.78302791135668</v>
       </c>
     </row>
     <row r="318" spans="1:11">
@@ -12362,10 +12362,10 @@
         <v>46209.24260416667</v>
       </c>
       <c r="J334">
-        <v>3.03138073350442</v>
+        <v>3.031380733504421</v>
       </c>
       <c r="K334">
-        <v>3.03138073350442</v>
+        <v>3.031380733504421</v>
       </c>
     </row>
     <row r="335" spans="1:11">
@@ -12782,10 +12782,10 @@
         <v>46223.11774305555</v>
       </c>
       <c r="J346">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
       <c r="K346">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
     </row>
     <row r="347" spans="1:11">
@@ -12887,10 +12887,10 @@
         <v>46223.11774305555</v>
       </c>
       <c r="J349">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
       <c r="K349">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
     </row>
     <row r="350" spans="1:11">
@@ -12992,10 +12992,10 @@
         <v>46221.7797337963</v>
       </c>
       <c r="J352">
-        <v>1.880842268464567</v>
+        <v>1.880842268464566</v>
       </c>
       <c r="K352">
-        <v>1.880842268464567</v>
+        <v>1.880842268464566</v>
       </c>
     </row>
     <row r="353" spans="1:11">
@@ -13132,10 +13132,10 @@
         <v>46221.7797337963</v>
       </c>
       <c r="J356">
-        <v>1.880842268464567</v>
+        <v>1.880842268464566</v>
       </c>
       <c r="K356">
-        <v>1.880842268464567</v>
+        <v>1.880842268464566</v>
       </c>
     </row>
     <row r="357" spans="1:11">
@@ -13202,10 +13202,10 @@
         <v>46223.50390046297</v>
       </c>
       <c r="J358">
-        <v>1.378209268297979</v>
+        <v>1.432079087253034</v>
       </c>
       <c r="K358">
-        <v>1.378209268297979</v>
+        <v>1.432079087253034</v>
       </c>
     </row>
     <row r="359" spans="1:11">
@@ -13272,10 +13272,10 @@
         <v>46223.50390046297</v>
       </c>
       <c r="J360">
-        <v>1.309772570875023</v>
+        <v>1.612532095135247</v>
       </c>
       <c r="K360">
-        <v>1.309772570875023</v>
+        <v>1.612532095135247</v>
       </c>
     </row>
     <row r="361" spans="1:11">
@@ -13377,10 +13377,10 @@
         <v>46223.50390046297</v>
       </c>
       <c r="J363">
-        <v>1.309772570875023</v>
+        <v>1.612532095135247</v>
       </c>
       <c r="K363">
-        <v>1.309772570875023</v>
+        <v>1.612532095135247</v>
       </c>
     </row>
     <row r="364" spans="1:11">

--- a/resources/M673/spc_cpk_detail.xlsx
+++ b/resources/M673/spc_cpk_detail.xlsx
@@ -1547,10 +1547,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J25">
-        <v>0.9608753676365078</v>
+        <v>0.9608753676365076</v>
       </c>
       <c r="K25">
-        <v>0.9608753676365078</v>
+        <v>0.9608753676365076</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1582,10 +1582,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J26">
-        <v>0.9608753676365078</v>
+        <v>0.9608753676365076</v>
       </c>
       <c r="K26">
-        <v>0.9608753676365078</v>
+        <v>0.9608753676365076</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1617,10 +1617,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J27">
-        <v>0.9608753676365078</v>
+        <v>0.9608753676365076</v>
       </c>
       <c r="K27">
-        <v>0.9608753676365078</v>
+        <v>0.9608753676365076</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3892,10 +3892,10 @@
         <v>46218.94015046296</v>
       </c>
       <c r="J92">
-        <v>3.235467172811132</v>
+        <v>3.235467172811131</v>
       </c>
       <c r="K92">
-        <v>3.235467172811132</v>
+        <v>3.235467172811131</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -4382,10 +4382,10 @@
         <v>46216.98412037037</v>
       </c>
       <c r="J106">
-        <v>2.103503458931062</v>
+        <v>2.103503458931063</v>
       </c>
       <c r="K106">
-        <v>2.103503458931062</v>
+        <v>2.103503458931063</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4662,10 +4662,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J114">
-        <v>3.363165505438486</v>
+        <v>3.363165505438485</v>
       </c>
       <c r="K114">
-        <v>3.363165505438486</v>
+        <v>3.363165505438485</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -4907,10 +4907,10 @@
         <v>46211.21850694445</v>
       </c>
       <c r="J121">
-        <v>3.74362915153003</v>
+        <v>3.743629151530029</v>
       </c>
       <c r="K121">
-        <v>3.74362915153003</v>
+        <v>3.743629151530029</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -5257,10 +5257,10 @@
         <v>46205.8512962963</v>
       </c>
       <c r="J131">
-        <v>1.787298381054459</v>
+        <v>1.787298381054458</v>
       </c>
       <c r="K131">
-        <v>1.787298381054459</v>
+        <v>1.787298381054458</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -5327,10 +5327,10 @@
         <v>46207.94072916666</v>
       </c>
       <c r="J133">
-        <v>2.191797453450521</v>
+        <v>2.191797453450522</v>
       </c>
       <c r="K133">
-        <v>2.191797453450521</v>
+        <v>2.191797453450522</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5817,10 +5817,10 @@
         <v>46205.8512962963</v>
       </c>
       <c r="J147">
-        <v>7.27129624353485</v>
+        <v>7.271296243534849</v>
       </c>
       <c r="K147">
-        <v>7.27129624353485</v>
+        <v>7.271296243534849</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -6167,10 +6167,10 @@
         <v>46219.73939814815</v>
       </c>
       <c r="J157">
-        <v>6.898914758144568</v>
+        <v>6.898914758144567</v>
       </c>
       <c r="K157">
-        <v>6.898914758144568</v>
+        <v>6.898914758144567</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -6202,10 +6202,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J158">
-        <v>6.497904288022408</v>
+        <v>6.497904288022409</v>
       </c>
       <c r="K158">
-        <v>6.497904288022408</v>
+        <v>6.497904288022409</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6377,10 +6377,10 @@
         <v>46205.8512962963</v>
       </c>
       <c r="J163">
-        <v>3.197210325160679</v>
+        <v>3.197210325160678</v>
       </c>
       <c r="K163">
-        <v>3.197210325160679</v>
+        <v>3.197210325160678</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -6727,10 +6727,10 @@
         <v>46219.73939814815</v>
       </c>
       <c r="J173">
-        <v>2.6636454511094</v>
+        <v>2.663645451109401</v>
       </c>
       <c r="K173">
-        <v>2.6636454511094</v>
+        <v>2.663645451109401</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -6832,10 +6832,10 @@
         <v>46208.97686342592</v>
       </c>
       <c r="J176">
-        <v>6.701960798400201</v>
+        <v>6.701960798400199</v>
       </c>
       <c r="K176">
-        <v>6.701960798400201</v>
+        <v>6.701960798400199</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -7602,10 +7602,10 @@
         <v>46209.56259259259</v>
       </c>
       <c r="J198">
-        <v>2.652272060164092</v>
+        <v>2.652272060164093</v>
       </c>
       <c r="K198">
-        <v>2.652272060164092</v>
+        <v>2.652272060164093</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -7952,10 +7952,10 @@
         <v>46220.03709490741</v>
       </c>
       <c r="J208">
-        <v>1.622592413978055</v>
+        <v>1.622592413978054</v>
       </c>
       <c r="K208">
-        <v>1.622592413978055</v>
+        <v>1.622592413978054</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -8057,10 +8057,10 @@
         <v>46207.86495370371</v>
       </c>
       <c r="J211">
-        <v>1.507303460676904</v>
+        <v>1.507303460676903</v>
       </c>
       <c r="K211">
-        <v>1.507303460676904</v>
+        <v>1.507303460676903</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -8232,10 +8232,10 @@
         <v>46217.99348379629</v>
       </c>
       <c r="J216">
-        <v>2.110247582543862</v>
+        <v>2.110247582543861</v>
       </c>
       <c r="K216">
-        <v>2.110247582543862</v>
+        <v>2.110247582543861</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -8407,10 +8407,10 @@
         <v>46208.97685185185</v>
       </c>
       <c r="J221">
-        <v>5.284726473752883</v>
+        <v>5.284726473752884</v>
       </c>
       <c r="K221">
-        <v>5.284726473752883</v>
+        <v>5.284726473752884</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -8617,10 +8617,10 @@
         <v>46208.97685185185</v>
       </c>
       <c r="J227">
-        <v>5.795279755351936</v>
+        <v>5.795279755351938</v>
       </c>
       <c r="K227">
-        <v>5.795279755351936</v>
+        <v>5.795279755351938</v>
       </c>
     </row>
     <row r="228" spans="1:11">
@@ -8722,10 +8722,10 @@
         <v>46211.14497685185</v>
       </c>
       <c r="J230">
-        <v>5.849518699950848</v>
+        <v>5.849518699950846</v>
       </c>
       <c r="K230">
-        <v>5.849518699950848</v>
+        <v>5.849518699950846</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -9212,10 +9212,10 @@
         <v>46210.99065972222</v>
       </c>
       <c r="J244">
-        <v>2.840609957198167</v>
+        <v>2.840609957198166</v>
       </c>
       <c r="K244">
-        <v>2.840609957198167</v>
+        <v>2.840609957198166</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -10367,10 +10367,10 @@
         <v>46218.99494212963</v>
       </c>
       <c r="J277">
-        <v>2.32304084432433</v>
+        <v>2.323040844324331</v>
       </c>
       <c r="K277">
-        <v>2.32304084432433</v>
+        <v>2.323040844324331</v>
       </c>
     </row>
     <row r="278" spans="1:11">
@@ -10577,10 +10577,10 @@
         <v>46220.03707175926</v>
       </c>
       <c r="J283">
-        <v>0.7867021626660747</v>
+        <v>0.7867021626660746</v>
       </c>
       <c r="K283">
-        <v>0.7867021626660747</v>
+        <v>0.7867021626660746</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -10647,10 +10647,10 @@
         <v>46206.94364583334</v>
       </c>
       <c r="J285">
-        <v>8.780808328949162</v>
+        <v>8.780808328949163</v>
       </c>
       <c r="K285">
-        <v>8.780808328949162</v>
+        <v>8.780808328949163</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -11662,10 +11662,10 @@
         <v>46224.64265046296</v>
       </c>
       <c r="J314">
-        <v>1.618078526923039</v>
+        <v>1.61807852692304</v>
       </c>
       <c r="K314">
-        <v>1.618078526923039</v>
+        <v>1.61807852692304</v>
       </c>
     </row>
     <row r="315" spans="1:11">
@@ -11697,10 +11697,10 @@
         <v>46208.79484953704</v>
       </c>
       <c r="J315">
-        <v>1.78302791135668</v>
+        <v>1.783027911356679</v>
       </c>
       <c r="K315">
-        <v>1.78302791135668</v>
+        <v>1.783027911356679</v>
       </c>
     </row>
     <row r="316" spans="1:11">
@@ -11767,10 +11767,10 @@
         <v>46208.79484953704</v>
       </c>
       <c r="J317">
-        <v>1.78302791135668</v>
+        <v>1.783027911356679</v>
       </c>
       <c r="K317">
-        <v>1.78302791135668</v>
+        <v>1.783027911356679</v>
       </c>
     </row>
     <row r="318" spans="1:11">
@@ -12362,10 +12362,10 @@
         <v>46209.24260416667</v>
       </c>
       <c r="J334">
-        <v>3.031380733504421</v>
+        <v>3.03138073350442</v>
       </c>
       <c r="K334">
-        <v>3.031380733504421</v>
+        <v>3.03138073350442</v>
       </c>
     </row>
     <row r="335" spans="1:11">
@@ -12782,10 +12782,10 @@
         <v>46223.11774305555</v>
       </c>
       <c r="J346">
-        <v>2.879589621422995</v>
+        <v>2.879589621422994</v>
       </c>
       <c r="K346">
-        <v>2.879589621422995</v>
+        <v>2.879589621422994</v>
       </c>
     </row>
     <row r="347" spans="1:11">
@@ -12887,10 +12887,10 @@
         <v>46223.11774305555</v>
       </c>
       <c r="J349">
-        <v>2.879589621422995</v>
+        <v>2.879589621422994</v>
       </c>
       <c r="K349">
-        <v>2.879589621422995</v>
+        <v>2.879589621422994</v>
       </c>
     </row>
     <row r="350" spans="1:11">
@@ -12992,10 +12992,10 @@
         <v>46221.7797337963</v>
       </c>
       <c r="J352">
-        <v>1.880842268464566</v>
+        <v>1.880842268464567</v>
       </c>
       <c r="K352">
-        <v>1.880842268464566</v>
+        <v>1.880842268464567</v>
       </c>
     </row>
     <row r="353" spans="1:11">
@@ -13132,10 +13132,10 @@
         <v>46221.7797337963</v>
       </c>
       <c r="J356">
-        <v>1.880842268464566</v>
+        <v>1.880842268464567</v>
       </c>
       <c r="K356">
-        <v>1.880842268464566</v>
+        <v>1.880842268464567</v>
       </c>
     </row>
     <row r="357" spans="1:11">

--- a/resources/M673/spc_cpk_detail.xlsx
+++ b/resources/M673/spc_cpk_detail.xlsx
@@ -1547,10 +1547,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J25">
-        <v>0.9608753676365076</v>
+        <v>0.9608753676365078</v>
       </c>
       <c r="K25">
-        <v>0.9608753676365076</v>
+        <v>0.9608753676365078</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1582,10 +1582,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J26">
-        <v>0.9608753676365076</v>
+        <v>0.9608753676365078</v>
       </c>
       <c r="K26">
-        <v>0.9608753676365076</v>
+        <v>0.9608753676365078</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1617,10 +1617,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J27">
-        <v>0.9608753676365076</v>
+        <v>0.9608753676365078</v>
       </c>
       <c r="K27">
-        <v>0.9608753676365076</v>
+        <v>0.9608753676365078</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1652,10 +1652,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J28">
-        <v>1.031451105176574</v>
+        <v>1.031451105176573</v>
       </c>
       <c r="K28">
-        <v>1.031451105176574</v>
+        <v>1.031451105176573</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1687,10 +1687,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J29">
-        <v>1.031451105176574</v>
+        <v>1.031451105176573</v>
       </c>
       <c r="K29">
-        <v>1.031451105176574</v>
+        <v>1.031451105176573</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1722,10 +1722,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J30">
-        <v>1.031451105176574</v>
+        <v>1.031451105176573</v>
       </c>
       <c r="K30">
-        <v>1.031451105176574</v>
+        <v>1.031451105176573</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1757,10 +1757,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J31">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
       <c r="K31">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1792,10 +1792,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J32">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
       <c r="K32">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1827,10 +1827,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J33">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
       <c r="K33">
-        <v>2.21028093512773</v>
+        <v>2.210280935127731</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3647,10 +3647,10 @@
         <v>46207.94072916666</v>
       </c>
       <c r="J85">
-        <v>2.894247413257619</v>
+        <v>2.894247413257618</v>
       </c>
       <c r="K85">
-        <v>2.894247413257619</v>
+        <v>2.894247413257618</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3787,10 +3787,10 @@
         <v>46211.21850694445</v>
       </c>
       <c r="J89">
-        <v>1.978021333216416</v>
+        <v>1.978021333216417</v>
       </c>
       <c r="K89">
-        <v>1.978021333216416</v>
+        <v>1.978021333216417</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3892,10 +3892,10 @@
         <v>46218.94015046296</v>
       </c>
       <c r="J92">
-        <v>3.235467172811131</v>
+        <v>3.235467172811132</v>
       </c>
       <c r="K92">
-        <v>3.235467172811131</v>
+        <v>3.235467172811132</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -4557,10 +4557,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J111">
-        <v>3.447537356994704</v>
+        <v>3.447537356994705</v>
       </c>
       <c r="K111">
-        <v>3.447537356994704</v>
+        <v>3.447537356994705</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4592,10 +4592,10 @@
         <v>46208.89827546296</v>
       </c>
       <c r="J112">
-        <v>3.758325112538279</v>
+        <v>3.758325112538278</v>
       </c>
       <c r="K112">
-        <v>3.758325112538279</v>
+        <v>3.758325112538278</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -4837,10 +4837,10 @@
         <v>46209.80684027778</v>
       </c>
       <c r="J119">
-        <v>4.241939324748978</v>
+        <v>4.241939324748977</v>
       </c>
       <c r="K119">
-        <v>4.241939324748978</v>
+        <v>4.241939324748977</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -4977,10 +4977,10 @@
         <v>46217.94935185185</v>
       </c>
       <c r="J123">
-        <v>3.700593491012436</v>
+        <v>3.700593491012435</v>
       </c>
       <c r="K123">
-        <v>3.700593491012436</v>
+        <v>3.700593491012435</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -5047,10 +5047,10 @@
         <v>46219.73939814815</v>
       </c>
       <c r="J125">
-        <v>4.109426526183723</v>
+        <v>4.109426526183722</v>
       </c>
       <c r="K125">
-        <v>4.109426526183723</v>
+        <v>4.109426526183722</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5327,10 +5327,10 @@
         <v>46207.94072916666</v>
       </c>
       <c r="J133">
-        <v>2.191797453450522</v>
+        <v>2.191797453450521</v>
       </c>
       <c r="K133">
-        <v>2.191797453450522</v>
+        <v>2.191797453450521</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5362,10 +5362,10 @@
         <v>46208.89827546296</v>
       </c>
       <c r="J134">
-        <v>2.219047446571034</v>
+        <v>2.219047446571033</v>
       </c>
       <c r="K134">
-        <v>2.219047446571034</v>
+        <v>2.219047446571033</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -6097,10 +6097,10 @@
         <v>46217.94935185185</v>
       </c>
       <c r="J155">
-        <v>5.499474884178864</v>
+        <v>5.499474884178865</v>
       </c>
       <c r="K155">
-        <v>5.499474884178864</v>
+        <v>5.499474884178865</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -6167,10 +6167,10 @@
         <v>46219.73939814815</v>
       </c>
       <c r="J157">
-        <v>6.898914758144567</v>
+        <v>6.898914758144568</v>
       </c>
       <c r="K157">
-        <v>6.898914758144567</v>
+        <v>6.898914758144568</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -6202,10 +6202,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J158">
-        <v>6.497904288022409</v>
+        <v>6.497904288022408</v>
       </c>
       <c r="K158">
-        <v>6.497904288022409</v>
+        <v>6.497904288022408</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6517,10 +6517,10 @@
         <v>46209.80684027778</v>
       </c>
       <c r="J167">
-        <v>2.611746366603724</v>
+        <v>2.611746366603725</v>
       </c>
       <c r="K167">
-        <v>2.611746366603724</v>
+        <v>2.611746366603725</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -6552,10 +6552,10 @@
         <v>46210.60912037037</v>
       </c>
       <c r="J168">
-        <v>2.16894508163721</v>
+        <v>2.168945081637211</v>
       </c>
       <c r="K168">
-        <v>2.16894508163721</v>
+        <v>2.168945081637211</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -6587,10 +6587,10 @@
         <v>46211.21850694445</v>
       </c>
       <c r="J169">
-        <v>2.462576987226219</v>
+        <v>2.46257698722622</v>
       </c>
       <c r="K169">
-        <v>2.462576987226219</v>
+        <v>2.46257698722622</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -6622,10 +6622,10 @@
         <v>46216.98412037037</v>
       </c>
       <c r="J170">
-        <v>2.727288952899633</v>
+        <v>2.727288952899634</v>
       </c>
       <c r="K170">
-        <v>2.727288952899633</v>
+        <v>2.727288952899634</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -7007,10 +7007,10 @@
         <v>46207.86495370371</v>
       </c>
       <c r="J181">
-        <v>5.998649854662134</v>
+        <v>5.998649854662133</v>
       </c>
       <c r="K181">
-        <v>5.998649854662134</v>
+        <v>5.998649854662133</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -7532,10 +7532,10 @@
         <v>46207.86495370371</v>
       </c>
       <c r="J196">
-        <v>1.932038980939303</v>
+        <v>1.932038980939302</v>
       </c>
       <c r="K196">
-        <v>1.932038980939303</v>
+        <v>1.932038980939302</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -8232,10 +8232,10 @@
         <v>46217.99348379629</v>
       </c>
       <c r="J216">
-        <v>2.110247582543861</v>
+        <v>2.110247582543862</v>
       </c>
       <c r="K216">
-        <v>2.110247582543861</v>
+        <v>2.110247582543862</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -8407,10 +8407,10 @@
         <v>46208.97685185185</v>
       </c>
       <c r="J221">
-        <v>5.284726473752884</v>
+        <v>5.284726473752883</v>
       </c>
       <c r="K221">
-        <v>5.284726473752884</v>
+        <v>5.284726473752883</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -8722,10 +8722,10 @@
         <v>46211.14497685185</v>
       </c>
       <c r="J230">
-        <v>5.849518699950846</v>
+        <v>5.849518699950848</v>
       </c>
       <c r="K230">
-        <v>5.849518699950846</v>
+        <v>5.849518699950848</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -8792,10 +8792,10 @@
         <v>46218.9949537037</v>
       </c>
       <c r="J232">
-        <v>5.012372322381821</v>
+        <v>5.01237232238182</v>
       </c>
       <c r="K232">
-        <v>5.012372322381821</v>
+        <v>5.01237232238182</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -9212,10 +9212,10 @@
         <v>46210.99065972222</v>
       </c>
       <c r="J244">
-        <v>2.840609957198166</v>
+        <v>2.840609957198167</v>
       </c>
       <c r="K244">
-        <v>2.840609957198166</v>
+        <v>2.840609957198167</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -9247,10 +9247,10 @@
         <v>46211.14497685185</v>
       </c>
       <c r="J245">
-        <v>3.592327472601819</v>
+        <v>3.592327472601818</v>
       </c>
       <c r="K245">
-        <v>3.592327472601819</v>
+        <v>3.592327472601818</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -10437,10 +10437,10 @@
         <v>46220.03707175926</v>
       </c>
       <c r="J279">
-        <v>3.373098742037829</v>
+        <v>3.37309874203783</v>
       </c>
       <c r="K279">
-        <v>3.373098742037829</v>
+        <v>3.37309874203783</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -10752,10 +10752,10 @@
         <v>46209.56256944445</v>
       </c>
       <c r="J288">
-        <v>7.300567584828319</v>
+        <v>7.30056758482832</v>
       </c>
       <c r="K288">
-        <v>7.300567584828319</v>
+        <v>7.30056758482832</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -11032,10 +11032,10 @@
         <v>46211.9912962963</v>
       </c>
       <c r="J296">
-        <v>1.665078177680939</v>
+        <v>1.66507817768094</v>
       </c>
       <c r="K296">
-        <v>1.665078177680939</v>
+        <v>1.66507817768094</v>
       </c>
     </row>
     <row r="297" spans="1:11">
@@ -11102,10 +11102,10 @@
         <v>46211.9912962963</v>
       </c>
       <c r="J298">
-        <v>1.665078177680939</v>
+        <v>1.66507817768094</v>
       </c>
       <c r="K298">
-        <v>1.665078177680939</v>
+        <v>1.66507817768094</v>
       </c>
     </row>
     <row r="299" spans="1:11">
@@ -12152,10 +12152,10 @@
         <v>46214.05010416666</v>
       </c>
       <c r="J328">
-        <v>3.459506744859925</v>
+        <v>3.459506744859926</v>
       </c>
       <c r="K328">
-        <v>3.459506744859925</v>
+        <v>3.459506744859926</v>
       </c>
     </row>
     <row r="329" spans="1:11">
@@ -12187,10 +12187,10 @@
         <v>46214.05010416666</v>
       </c>
       <c r="J329">
-        <v>3.459506744859925</v>
+        <v>3.459506744859926</v>
       </c>
       <c r="K329">
-        <v>3.459506744859925</v>
+        <v>3.459506744859926</v>
       </c>
     </row>
     <row r="330" spans="1:11">
@@ -12782,10 +12782,10 @@
         <v>46223.11774305555</v>
       </c>
       <c r="J346">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
       <c r="K346">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
     </row>
     <row r="347" spans="1:11">
@@ -12887,10 +12887,10 @@
         <v>46223.11774305555</v>
       </c>
       <c r="J349">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
       <c r="K349">
-        <v>2.879589621422994</v>
+        <v>2.879589621422995</v>
       </c>
     </row>
     <row r="350" spans="1:11">

--- a/resources/M673/spc_cpk_detail.xlsx
+++ b/resources/M673/spc_cpk_detail.xlsx
@@ -1442,10 +1442,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J22">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
       <c r="K22">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1477,10 +1477,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J23">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
       <c r="K23">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1512,10 +1512,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J24">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
       <c r="K24">
-        <v>0.952594830358694</v>
+        <v>0.9525948303586942</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1652,10 +1652,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J28">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
       <c r="K28">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1687,10 +1687,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J29">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
       <c r="K29">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1722,10 +1722,10 @@
         <v>46207.84418981482</v>
       </c>
       <c r="J30">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
       <c r="K30">
-        <v>1.031451105176573</v>
+        <v>1.031451105176574</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1757,10 +1757,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J31">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
       <c r="K31">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1792,10 +1792,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J32">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
       <c r="K32">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1827,10 +1827,10 @@
         <v>46207.88630787037</v>
       </c>
       <c r="J33">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
       <c r="K33">
-        <v>2.210280935127731</v>
+        <v>2.21028093512773</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2597,10 +2597,10 @@
         <v>46208.36424768518</v>
       </c>
       <c r="J55">
-        <v>2.200650529645804</v>
+        <v>2.200650529645805</v>
       </c>
       <c r="K55">
-        <v>2.200650529645804</v>
+        <v>2.200650529645805</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2632,10 +2632,10 @@
         <v>46208.36424768518</v>
       </c>
       <c r="J56">
-        <v>2.200650529645804</v>
+        <v>2.200650529645805</v>
       </c>
       <c r="K56">
-        <v>2.200650529645804</v>
+        <v>2.200650529645805</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2667,10 +2667,10 @@
         <v>46208.36424768518</v>
       </c>
       <c r="J57">
-        <v>2.200650529645804</v>
+        <v>2.200650529645805</v>
       </c>
       <c r="K57">
-        <v>2.200650529645804</v>
+        <v>2.200650529645805</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -3647,10 +3647,10 @@
         <v>46207.94072916666</v>
       </c>
       <c r="J85">
-        <v>2.894247413257618</v>
+        <v>2.894247413257619</v>
       </c>
       <c r="K85">
-        <v>2.894247413257618</v>
+        <v>2.894247413257619</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4557,10 +4557,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J111">
-        <v>3.447537356994705</v>
+        <v>3.447537356994704</v>
       </c>
       <c r="K111">
-        <v>3.447537356994705</v>
+        <v>3.447537356994704</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4907,10 +4907,10 @@
         <v>46211.21850694445</v>
       </c>
       <c r="J121">
-        <v>3.743629151530029</v>
+        <v>3.74362915153003</v>
       </c>
       <c r="K121">
-        <v>3.743629151530029</v>
+        <v>3.74362915153003</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -5362,10 +5362,10 @@
         <v>46208.89827546296</v>
       </c>
       <c r="J134">
-        <v>2.219047446571033</v>
+        <v>2.219047446571034</v>
       </c>
       <c r="K134">
-        <v>2.219047446571033</v>
+        <v>2.219047446571034</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -5817,10 +5817,10 @@
         <v>46205.8512962963</v>
       </c>
       <c r="J147">
-        <v>7.271296243534849</v>
+        <v>7.271296243534847</v>
       </c>
       <c r="K147">
-        <v>7.271296243534849</v>
+        <v>7.271296243534847</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -6167,10 +6167,10 @@
         <v>46219.73939814815</v>
       </c>
       <c r="J157">
-        <v>6.898914758144568</v>
+        <v>6.898914758144567</v>
       </c>
       <c r="K157">
-        <v>6.898914758144568</v>
+        <v>6.898914758144567</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -6202,10 +6202,10 @@
         <v>46220.18728009259</v>
       </c>
       <c r="J158">
-        <v>6.497904288022408</v>
+        <v>6.497904288022409</v>
       </c>
       <c r="K158">
-        <v>6.497904288022408</v>
+        <v>6.497904288022409</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6587,10 +6587,10 @@
         <v>46211.21850694445</v>
       </c>
       <c r="J169">
-        <v>2.46257698722622</v>
+        <v>2.462576987226219</v>
       </c>
       <c r="K169">
-        <v>2.46257698722622</v>
+        <v>2.462576987226219</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -6832,10 +6832,10 @@
         <v>46208.97686342592</v>
       </c>
       <c r="J176">
-        <v>6.701960798400199</v>
+        <v>6.701960798400201</v>
       </c>
       <c r="K176">
-        <v>6.701960798400199</v>
+        <v>6.701960798400201</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -6972,10 +6972,10 @@
         <v>46206.94366898148</v>
       </c>
       <c r="J180">
-        <v>7.075559370742078</v>
+        <v>7.075559370742076</v>
       </c>
       <c r="K180">
-        <v>7.075559370742078</v>
+        <v>7.075559370742076</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -7007,10 +7007,10 @@
         <v>46207.86495370371</v>
       </c>
       <c r="J181">
-        <v>5.998649854662133</v>
+        <v>5.998649854662134</v>
       </c>
       <c r="K181">
-        <v>5.998649854662133</v>
+        <v>5.998649854662134</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -7532,10 +7532,10 @@
         <v>46207.86495370371</v>
       </c>
       <c r="J196">
-        <v>1.932038980939302</v>
+        <v>1.932038980939303</v>
       </c>
       <c r="K196">
-        <v>1.932038980939302</v>
+        <v>1.932038980939303</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -7882,10 +7882,10 @@
         <v>46208.97686342592</v>
       </c>
       <c r="J206">
-        <v>1.46674596671112</v>
+        <v>1.466745966711119</v>
       </c>
       <c r="K206">
-        <v>1.46674596671112</v>
+        <v>1.466745966711119</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -8232,10 +8232,10 @@
         <v>46217.99348379629</v>
       </c>
       <c r="J216">
-        <v>2.110247582543862</v>
+        <v>2.110247582543861</v>
       </c>
       <c r="K216">
-        <v>2.110247582543862</v>
+        <v>2.110247582543861</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -8407,10 +8407,10 @@
         <v>46208.97685185185</v>
       </c>
       <c r="J221">
-        <v>5.284726473752883</v>
+        <v>5.284726473752884</v>
       </c>
       <c r="K221">
-        <v>5.284726473752883</v>
+        <v>5.284726473752884</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -8722,10 +8722,10 @@
         <v>46211.14497685185</v>
       </c>
       <c r="J230">
-        <v>5.849518699950848</v>
+        <v>5.849518699950846</v>
       </c>
       <c r="K230">
-        <v>5.849518699950848</v>
+        <v>5.849518699950846</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -8792,10 +8792,10 @@
         <v>46218.9949537037</v>
       </c>
       <c r="J232">
-        <v>5.01237232238182</v>
+        <v>5.012372322381821</v>
       </c>
       <c r="K232">
-        <v>5.01237232238182</v>
+        <v>5.012372322381821</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -9037,10 +9037,10 @@
         <v>46205.79703703704</v>
       </c>
       <c r="J239">
-        <v>3.228053567897934</v>
+        <v>3.228053567897933</v>
       </c>
       <c r="K239">
-        <v>3.228053567897934</v>
+        <v>3.228053567897933</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -9107,10 +9107,10 @@
         <v>46207.86494212963</v>
       </c>
       <c r="J241">
-        <v>3.005825928238067</v>
+        <v>3.005825928238066</v>
       </c>
       <c r="K241">
-        <v>3.005825928238067</v>
+        <v>3.005825928238066</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -9212,10 +9212,10 @@
         <v>46210.99065972222</v>
       </c>
       <c r="J244">
-        <v>2.840609957198167</v>
+        <v>2.840609957198166</v>
       </c>
       <c r="K244">
-        <v>2.840609957198167</v>
+        <v>2.840609957198166</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -9247,10 +9247,10 @@
         <v>46211.14497685185</v>
       </c>
       <c r="J245">
-        <v>3.592327472601818</v>
+        <v>3.592327472601819</v>
       </c>
       <c r="K245">
-        <v>3.592327472601818</v>
+        <v>3.592327472601819</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -9387,10 +9387,10 @@
         <v>46220.03708333334</v>
       </c>
       <c r="J249">
-        <v>2.866682293405833</v>
+        <v>2.866682293405832</v>
       </c>
       <c r="K249">
-        <v>2.866682293405833</v>
+        <v>2.866682293405832</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -10367,10 +10367,10 @@
         <v>46218.99494212963</v>
       </c>
       <c r="J277">
-        <v>2.323040844324331</v>
+        <v>2.32304084432433</v>
       </c>
       <c r="K277">
-        <v>2.323040844324331</v>
+        <v>2.32304084432433</v>
       </c>
     </row>
     <row r="278" spans="1:11">
@@ -10682,10 +10682,10 @@
         <v>46207.86493055556</v>
       </c>
       <c r="J286">
-        <v>7.428547053050218</v>
+        <v>7.428547053050217</v>
       </c>
       <c r="K286">
-        <v>7.428547053050218</v>
+        <v>7.428547053050217</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -10752,10 +10752,10 @@
         <v>46209.56256944445</v>
       </c>
       <c r="J288">
-        <v>7.30056758482832</v>
+        <v>7.300567584828319</v>
       </c>
       <c r="K288">
-        <v>7.30056758482832</v>
+        <v>7.300567584828319</v>
       </c>
     </row>
     <row r="289" spans="1:11">
